--- a/src/global/utils/file-utils/locators.xlsx
+++ b/src/global/utils/file-utils/locators.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="322">
   <si>
     <t>page</t>
   </si>
@@ -37,7 +37,7 @@
     <t>options</t>
   </si>
   <si>
-    <t>nth_x000d_</t>
+    <t>nth_x000D_</t>
   </si>
   <si>
     <t>updatePassword</t>
@@ -55,7 +55,7 @@
     <t>{"name":"Deposit"}</t>
   </si>
   <si>
-    <t>0_x000d_</t>
+    <t>0_x000D_</t>
   </si>
   <si>
     <t>updatePasswordButton</t>
@@ -142,10 +142,10 @@
     <t>UPDATE PASSWORD</t>
   </si>
   <si>
-    <t>2_x000d_</t>
-  </si>
-  <si>
-    <t>_x000d_</t>
+    <t>2_x000D_</t>
+  </si>
+  <si>
+    <t>_x000D_</t>
   </si>
   <si>
     <t>limits</t>
@@ -400,7 +400,7 @@
     <t>columnHeaders</t>
   </si>
   <si>
-    <t>thead th</t>
+    <t>td.cell-width:has-text("{headerName}")</t>
   </si>
   <si>
     <t>showDetailIcon</t>
@@ -430,7 +430,7 @@
     <t>pageNumbers</t>
   </si>
   <si>
-    <t>.pagination</t>
+    <t>div.sticky.bottom-0 div.border-1.std-border</t>
   </si>
   <si>
     <t>goToPageEllipsis</t>
@@ -508,7 +508,7 @@
     <t>searchInput</t>
   </si>
   <si>
-    <t>{"name":"Search games"}</t>
+    <t>[element-name="nav-bar-search"]</t>
   </si>
   <si>
     <t>loginCTA</t>
@@ -568,6 +568,12 @@
     <t>{"name":"password"}</t>
   </si>
   <si>
+    <t>actualSearchInput</t>
+  </si>
+  <si>
+    <t>#search</t>
+  </si>
+  <si>
     <t>submitLoginButton</t>
   </si>
   <si>
@@ -589,9 +595,6 @@
     <t>searchField</t>
   </si>
   <si>
-    <t>[element-name="nav-bar-search"]</t>
-  </si>
-  <si>
     <t>promotionsCTA</t>
   </si>
   <si>
@@ -619,43 +622,43 @@
     <t>quickLinksDropdown</t>
   </si>
   <si>
-    <t>{"name":"Quick Links"}</t>
+    <t>summary:has-text("Quick Links")</t>
   </si>
   <si>
     <t>privacyPolicyCTA</t>
   </si>
   <si>
-    <t>{"name":"Privacy Policy"}</t>
+    <t>details:has(summary:has-text("Quick Links")) a[href="/privacy-policy"]</t>
   </si>
   <si>
     <t>contactUsCTA</t>
   </si>
   <si>
-    <t>{"name":"Contact Us"}</t>
+    <t>details:has(summary:has-text("Quick Links")) a[href="/contact-us"]</t>
   </si>
   <si>
     <t>termsConditionsCTA</t>
   </si>
   <si>
-    <t>{"name":"Terms &amp; Conditions"}</t>
+    <t>details:has(summary:has-text("Quick Links")) a[href="/terms-and-conditions"]</t>
   </si>
   <si>
     <t>faqsCTA</t>
   </si>
   <si>
-    <t>{"name":"FAQ&amp;apos;s"}</t>
+    <t>details:has(summary:has-text("Quick Links")) a[href="/faq"]</t>
   </si>
   <si>
     <t>responsibleGamblingCTA</t>
   </si>
   <si>
-    <t>{"name":"Responsible Gambling"}</t>
+    <t>details:has(summary:has-text("Quick Links")) a[href="/responsible-gambling"]</t>
   </si>
   <si>
     <t>getTheAppCTA</t>
   </si>
   <si>
-    <t>{"name":"Get the app"}</t>
+    <t>details:has(summary:has-text("Quick Links")) a[href="/get-the-app"]</t>
   </si>
   <si>
     <t>slotGamesCategory</t>
@@ -694,13 +697,13 @@
     <t>{"name":"Jackpotcity Huawei App"}</t>
   </si>
   <si>
-    <t>.bg-primary-layer</t>
+    <t>div:has-text("Welcome,")</t>
   </si>
   <si>
     <t>balanceContainer</t>
   </si>
   <si>
-    <t>div:has-text("Cash"):has-text("Bonus Balance")</t>
+    <t>div.flex-col:has(div:has-text("Cash")):has(div:has-text("Bonus Balance"))</t>
   </si>
   <si>
     <t>cashBalance</t>
@@ -718,10 +721,10 @@
     <t>accountNo</t>
   </si>
   <si>
-    <t>.bg-primary-layer &gt;&gt; text=Account No: &gt;&gt; ..</t>
-  </si>
-  <si>
-    <t>.design-system-button.flex.items-center.font-bold.hover\:cursor-pointer.hover\:shadow-md.text-base-priority.p-0</t>
+    <t>div.truncate:has-text("Account No:")</t>
+  </si>
+  <si>
+    <t>button:has-text("Deposit") + button</t>
   </si>
   <si>
     <t>withdrawalCTA</t>
@@ -736,70 +739,73 @@
     <t>myAccountDropdown</t>
   </si>
   <si>
-    <t>{"name":"My Account"}</t>
+    <t>summary:has-text("My Account")</t>
   </si>
   <si>
     <t>myAccountRegion</t>
   </si>
   <si>
-    <t>region</t>
+    <t>details:has(summary:has-text("My Account"))</t>
   </si>
   <si>
     <t>myAccountDeposit</t>
   </si>
   <si>
+    <t>details:has(summary:has-text("My Account")) div.cursor-pointer:has-text("Deposit")</t>
+  </si>
+  <si>
     <t>myAccountWithdrawal</t>
   </si>
   <si>
-    <t>{"name":"Withdrawal"}</t>
+    <t>details:has(summary:has-text("My Account")) div.cursor-pointer:has-text("Withdrawal")</t>
   </si>
   <si>
     <t>transactionSummaryCTA</t>
   </si>
   <si>
-    <t>{"name":"Transaction Summary"}</t>
+    <t>details:has(summary:has-text("My Account")) div.cursor-pointer:has-text("Transaction Summary")</t>
   </si>
   <si>
     <t>bonusWalletCTA</t>
   </si>
   <si>
-    <t>{"name":"Bonus Wallet"}</t>
+    <t>details:has(summary:has-text("My Account")) div.cursor-pointer:has-text("Bonus Wallet")</t>
   </si>
   <si>
     <t>personalDetailsCTA</t>
   </si>
   <si>
-    <t>{"name":"Personal Details"}</t>
+    <t>details:has(summary:has-text("My Account")) div.cursor-pointer:has-text("My Profile Management")</t>
   </si>
   <si>
     <t>accountSettingsCTA</t>
   </si>
   <si>
-    <t>{"name":"Account Settings"}</t>
+    <t>details:has(summary:has-text("My Account")) div.cursor-pointer:has-text("Account Settings")</t>
   </si>
   <si>
     <t>updatePasswordCTA</t>
   </si>
   <si>
-    <t>{"name":"Update Password"}</t>
+    <t>details:has(summary:has-text("My Account")) div.cursor-pointer:has-text("Update Password")</t>
   </si>
   <si>
     <t>responsibleGamingCTA</t>
   </si>
   <si>
-    <t>{"name":"Responsible Gaming"}</t>
+    <t>details:has(summary:has-text("My Account")) div.cursor-pointer:has-text("Responsible Gaming")</t>
   </si>
   <si>
     <t>documentVerificationCTA</t>
   </si>
   <si>
-    <t>{"name":"Document Verification"}</t>
+    <t>details:has(summary:has-text("My Account")) div.cursor-pointer:has-text("Document Verification")</t>
   </si>
   <si>
     <t>logOutCTA</t>
   </si>
   <si>
-    <t>{"name":"Log Out"}</t>
+    <t>details:has(summary:has-text("My Account")) div.cursor-pointer:has-text("Log out")</t>
   </si>
   <si>
     <t>slotGamesCTA</t>
@@ -811,10 +817,13 @@
     <t>div:has-text("Game Categories") &gt;&gt; text="Betgames"</t>
   </si>
   <si>
-    <t>quickGamesCTA</t>
-  </si>
-  <si>
-    <t>div:has-text("Game Categories") &gt;&gt; text="Quick Games"</t>
+    <t>details:has(summary:has-text("My Account")) div:has-text("Bonus Wallet")</t>
+  </si>
+  <si>
+    <t>cityRewardsCTA</t>
+  </si>
+  <si>
+    <t>details:has(summary:has-text("My Account")) div:has-text("City Rewards")</t>
   </si>
   <si>
     <t>login</t>
@@ -994,13 +1003,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1032,7 +1041,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -1043,9 +1052,6 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1053,9 +1059,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1366,9 +1372,9 @@
     <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="2" width="16.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="28.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="5" width="28.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="2" width="37.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -1393,10 +1399,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>8</v>
@@ -1413,10 +1419,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
@@ -1433,10 +1439,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>8</v>
@@ -1453,7 +1459,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>21</v>
@@ -1465,7 +1471,7 @@
         <v>22</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F5" s="4">
         <v>0</v>
@@ -1473,10 +1479,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>8</v>
@@ -1485,7 +1491,7 @@
         <v>22</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F6" s="4">
         <v>0</v>
@@ -1493,10 +1499,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>8</v>
@@ -1505,7 +1511,7 @@
         <v>22</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F7" s="4">
         <v>0</v>
@@ -1513,10 +1519,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>8</v>
@@ -1525,7 +1531,7 @@
         <v>22</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F8" s="4">
         <v>0</v>
@@ -1533,10 +1539,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>8</v>
@@ -1545,7 +1551,7 @@
         <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F9" s="4">
         <v>0</v>
@@ -1553,10 +1559,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>8</v>
@@ -1565,7 +1571,7 @@
         <v>96</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F10" s="4">
         <v>0</v>
@@ -1573,16 +1579,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>17</v>
@@ -1593,16 +1599,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>17</v>
@@ -1613,10 +1619,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>8</v>
@@ -1625,7 +1631,7 @@
         <v>22</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F13" s="4">
         <v>0</v>
@@ -1633,10 +1639,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>8</v>
@@ -1645,7 +1651,7 @@
         <v>22</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F14" s="4">
         <v>0</v>
@@ -1653,10 +1659,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>8</v>
@@ -1665,7 +1671,7 @@
         <v>96</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F15" s="4">
         <v>0</v>
@@ -1673,15 +1679,15 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="D16" s="8">
+        <v>309</v>
+      </c>
+      <c r="D16" s="7">
         <v>46151</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -1693,10 +1699,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>8</v>
@@ -1705,7 +1711,7 @@
         <v>96</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F17" s="4">
         <v>0</v>
@@ -1713,16 +1719,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>17</v>
@@ -1733,19 +1739,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F19" s="4">
         <v>0</v>
@@ -1753,19 +1759,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F20" s="4">
         <v>0</v>
@@ -1773,10 +1779,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>8</v>
@@ -1785,7 +1791,7 @@
         <v>9</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F21" s="4">
         <v>0</v>
@@ -1793,10 +1799,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>19</v>
@@ -1854,10 +1860,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>8</v>
@@ -1874,10 +1880,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
@@ -1894,10 +1900,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>8</v>
@@ -1909,15 +1915,15 @@
         <v>164</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>8</v>
@@ -1934,16 +1940,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>17</v>
@@ -1954,10 +1960,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>8</v>
@@ -1966,7 +1972,7 @@
         <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>86</v>
@@ -1974,16 +1980,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>17</v>
@@ -1994,16 +2000,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>17</v>
@@ -2014,7 +2020,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>179</v>
@@ -2034,7 +2040,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>21</v>
@@ -2054,16 +2060,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>17</v>
@@ -2074,10 +2080,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>19</v>
@@ -2102,18 +2108,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="2" width="19.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="34.29071428571429" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="79.005" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="2" width="31.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2133,9 +2139,9 @@
         <v>87</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>89</v>
@@ -2153,12 +2159,12 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>15</v>
@@ -2169,38 +2175,38 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="A5" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="B5" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>17</v>
@@ -2211,16 +2217,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>17</v>
@@ -2231,16 +2237,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>17</v>
@@ -2251,16 +2257,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>17</v>
@@ -2271,16 +2277,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>17</v>
@@ -2291,19 +2297,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>9</v>
+        <v>200</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>199</v>
+        <v>17</v>
       </c>
       <c r="F10" s="4">
         <v>0</v>
@@ -2311,136 +2317,136 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>9</v>
+        <v>202</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>201</v>
+        <v>17</v>
       </c>
       <c r="F11" s="4">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>9</v>
+        <v>204</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>203</v>
+        <v>17</v>
       </c>
       <c r="F12" s="4">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>9</v>
+        <v>206</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>205</v>
+        <v>17</v>
       </c>
       <c r="F13" s="4">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>9</v>
+        <v>208</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="F14" s="4">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>9</v>
+        <v>210</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>209</v>
+        <v>17</v>
       </c>
       <c r="F15" s="4">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>9</v>
+        <v>212</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>211</v>
+        <v>17</v>
       </c>
       <c r="F16" s="4">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>17</v>
@@ -2449,18 +2455,18 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>17</v>
@@ -2469,18 +2475,18 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>17</v>
@@ -2489,12 +2495,12 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>8</v>
@@ -2503,18 +2509,18 @@
         <v>9</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F20" s="4">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>8</v>
@@ -2523,18 +2529,18 @@
         <v>9</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F21" s="4">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>8</v>
@@ -2543,15 +2549,15 @@
         <v>9</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F22" s="4">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>171</v>
@@ -2560,7 +2566,7 @@
         <v>15</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>17</v>
@@ -2569,18 +2575,18 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>17</v>
@@ -2589,18 +2595,18 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>17</v>
@@ -2609,18 +2615,18 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>17</v>
@@ -2629,9 +2635,9 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
@@ -2649,18 +2655,18 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>17</v>
@@ -2669,9 +2675,9 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>26</v>
@@ -2680,7 +2686,7 @@
         <v>15</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>17</v>
@@ -2689,201 +2695,201 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F30" s="4">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>9</v>
+        <v>239</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>238</v>
+        <v>17</v>
       </c>
       <c r="F31" s="4">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>238</v>
+        <v>17</v>
       </c>
       <c r="F32" s="4">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>9</v>
+        <v>243</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F33" s="4">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>243</v>
+        <v>17</v>
       </c>
       <c r="F34" s="4">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>9</v>
+        <v>247</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>245</v>
+        <v>17</v>
       </c>
       <c r="F35" s="4">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>9</v>
+        <v>249</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>247</v>
+        <v>17</v>
       </c>
       <c r="F36" s="4">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>9</v>
+        <v>251</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>249</v>
+        <v>17</v>
       </c>
       <c r="F37" s="4">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>9</v>
+        <v>253</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>251</v>
+        <v>17</v>
       </c>
       <c r="F38" s="4">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
       <c r="A39" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>9</v>
+        <v>255</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>253</v>
+        <v>17</v>
       </c>
       <c r="F39" s="4">
         <v>0</v>
@@ -2891,19 +2897,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>9</v>
+        <v>257</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>255</v>
+        <v>17</v>
       </c>
       <c r="F40" s="4">
         <v>0</v>
@@ -2911,19 +2917,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>9</v>
+        <v>259</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>257</v>
+        <v>17</v>
       </c>
       <c r="F41" s="4">
         <v>0</v>
@@ -2931,19 +2937,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>9</v>
+        <v>261</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>259</v>
+        <v>17</v>
       </c>
       <c r="F42" s="4">
         <v>0</v>
@@ -2951,16 +2957,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>17</v>
@@ -2971,16 +2977,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>17</v>
@@ -2991,22 +2997,42 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F45" s="4">
-        <v>0</v>
+      <c r="F45" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+      <c r="A46" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" s="4">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3019,14 +3045,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -3042,7 +3068,7 @@
       <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="3" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3102,13 +3128,13 @@
         <v>161</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>162</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>162</v>
+        <v>17</v>
       </c>
       <c r="E5" s="4">
         <v>0</v>
@@ -3289,15 +3315,32 @@
         <v>182</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E16" s="4">
+      <c r="D17" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E17" s="4">
         <v>0</v>
       </c>
     </row>
@@ -3319,7 +3362,7 @@
     <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="2" width="66.29071428571429" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="2" width="42.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -3462,7 +3505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1" t="s">
         <v>88</v>
       </c>
@@ -3482,7 +3525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="1" t="s">
         <v>88</v>
       </c>
@@ -3502,7 +3545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="1" t="s">
         <v>88</v>
       </c>
@@ -3522,7 +3565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="1" t="s">
         <v>88</v>
       </c>
@@ -3962,7 +4005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="1" t="s">
         <v>88</v>
       </c>
@@ -3978,7 +4021,7 @@
       <c r="E33" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="4">
         <v>0</v>
       </c>
     </row>
